--- a/artfynd/A 31658-2025 artfynd.xlsx
+++ b/artfynd/A 31658-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126580820</v>
       </c>
       <c r="B2" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126580644</v>
       </c>
       <c r="B4" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126580350</v>
       </c>
       <c r="B5" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>126580821</v>
       </c>
       <c r="B6" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>126580435</v>
       </c>
       <c r="B7" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>126580838</v>
       </c>
       <c r="B8" t="n">
-        <v>77929</v>
+        <v>77989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>126580645</v>
       </c>
       <c r="B9" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>126580822</v>
       </c>
       <c r="B10" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126580593</v>
+        <v>126580579</v>
       </c>
       <c r="B11" t="n">
-        <v>92727</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,34 +1569,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tallberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386258</v>
+        <v>386260</v>
       </c>
       <c r="R11" t="n">
-        <v>6842760</v>
+        <v>6842745</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,6 +1634,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126580579</v>
+        <v>126580593</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>92802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,39 +1676,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tallberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386260</v>
+        <v>386258</v>
       </c>
       <c r="R12" t="n">
-        <v>6842745</v>
+        <v>6842760</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,11 +1736,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1765,7 +1765,7 @@
         <v>126580646</v>
       </c>
       <c r="B13" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>126580851</v>
       </c>
       <c r="B15" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>126580355</v>
       </c>
       <c r="B16" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>126580353</v>
       </c>
       <c r="B17" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>126580464</v>
       </c>
       <c r="B19" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 31658-2025 artfynd.xlsx
+++ b/artfynd/A 31658-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126580820</v>
       </c>
       <c r="B2" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126580644</v>
+        <v>126580350</v>
       </c>
       <c r="B4" t="n">
-        <v>78770</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386233</v>
+        <v>386300</v>
       </c>
       <c r="R4" t="n">
-        <v>6842685</v>
+        <v>6842755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126580350</v>
+        <v>126580644</v>
       </c>
       <c r="B5" t="n">
-        <v>79629</v>
+        <v>78773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386300</v>
+        <v>386233</v>
       </c>
       <c r="R5" t="n">
-        <v>6842755</v>
+        <v>6842685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
         <v>126580821</v>
       </c>
       <c r="B6" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>126580435</v>
       </c>
       <c r="B7" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>126580838</v>
       </c>
       <c r="B8" t="n">
-        <v>77989</v>
+        <v>77992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>126580645</v>
       </c>
       <c r="B9" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>126580822</v>
       </c>
       <c r="B10" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126580579</v>
+        <v>126580593</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>92808</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,39 +1569,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tallberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386260</v>
+        <v>386258</v>
       </c>
       <c r="R11" t="n">
-        <v>6842745</v>
+        <v>6842760</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126580593</v>
+        <v>126580579</v>
       </c>
       <c r="B12" t="n">
-        <v>92802</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,34 +1666,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tallberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386258</v>
+        <v>386260</v>
       </c>
       <c r="R12" t="n">
-        <v>6842760</v>
+        <v>6842745</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,6 +1731,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1765,7 +1765,7 @@
         <v>126580646</v>
       </c>
       <c r="B13" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>126580851</v>
       </c>
       <c r="B15" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>126580355</v>
       </c>
       <c r="B16" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>126580353</v>
       </c>
       <c r="B17" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>126580464</v>
       </c>
       <c r="B19" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 31658-2025 artfynd.xlsx
+++ b/artfynd/A 31658-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126580820</v>
       </c>
       <c r="B2" t="n">
-        <v>78681</v>
+        <v>78678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126580350</v>
+        <v>126580644</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>78770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386300</v>
+        <v>386233</v>
       </c>
       <c r="R4" t="n">
-        <v>6842755</v>
+        <v>6842685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126580644</v>
+        <v>126580350</v>
       </c>
       <c r="B5" t="n">
-        <v>78773</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386233</v>
+        <v>386300</v>
       </c>
       <c r="R5" t="n">
-        <v>6842685</v>
+        <v>6842755</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
         <v>126580821</v>
       </c>
       <c r="B6" t="n">
-        <v>78681</v>
+        <v>78678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>126580435</v>
       </c>
       <c r="B7" t="n">
-        <v>91290</v>
+        <v>91284</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>126580838</v>
       </c>
       <c r="B8" t="n">
-        <v>77992</v>
+        <v>77989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>126580645</v>
       </c>
       <c r="B9" t="n">
-        <v>78773</v>
+        <v>78770</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>126580822</v>
       </c>
       <c r="B10" t="n">
-        <v>78681</v>
+        <v>78678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126580593</v>
+        <v>126580579</v>
       </c>
       <c r="B11" t="n">
-        <v>92808</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,34 +1569,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tallberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386258</v>
+        <v>386260</v>
       </c>
       <c r="R11" t="n">
-        <v>6842760</v>
+        <v>6842745</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,6 +1634,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126580579</v>
+        <v>126580593</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>92802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,39 +1676,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tallberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386260</v>
+        <v>386258</v>
       </c>
       <c r="R12" t="n">
-        <v>6842745</v>
+        <v>6842760</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,11 +1736,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1765,7 +1765,7 @@
         <v>126580646</v>
       </c>
       <c r="B13" t="n">
-        <v>78773</v>
+        <v>78770</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>126580851</v>
       </c>
       <c r="B15" t="n">
-        <v>78420</v>
+        <v>78417</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>126580355</v>
       </c>
       <c r="B16" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>126580353</v>
       </c>
       <c r="B17" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>126580464</v>
       </c>
       <c r="B19" t="n">
-        <v>79603</v>
+        <v>79600</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 31658-2025 artfynd.xlsx
+++ b/artfynd/A 31658-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580820</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580821</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580822</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580593</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580568</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580435</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580436</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580851</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580693</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580350</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580352</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580353</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580355</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580356</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580358</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580360</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580838</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580579</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2535,6 +2630,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580583</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2636,6 +2736,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580531</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2733,6 +2838,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580537</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2830,6 +2940,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580644</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2927,6 +3042,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580645</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3024,6 +3144,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580646</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3121,6 +3246,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580463</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3218,6 +3348,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580464</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3315,8 +3450,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580465</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>